--- a/Simulation/Results/p.mid_Ten.Fixed.Ints_mean.surv.30.xlsx
+++ b/Simulation/Results/p.mid_Ten.Fixed.Ints_mean.surv.30.xlsx
@@ -47,16 +47,16 @@
     <t xml:space="preserve">mid</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7 mins</t>
+    <t xml:space="preserve">5.3 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 hours</t>
   </si>
 </sst>
 </file>
@@ -419,13 +419,13 @@
         <v>50</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0219</v>
+        <v>0.0203</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0175</v>
+        <v>0.0155</v>
       </c>
       <c r="D2" t="n">
-        <v>0.041</v>
+        <v>0.036</v>
       </c>
       <c r="E2" t="n">
         <v>0.0333333333333333</v>
@@ -448,13 +448,13 @@
         <v>100</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0336</v>
+        <v>0.0313</v>
       </c>
       <c r="C3" t="n">
-        <v>0.034</v>
+        <v>0.0329</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0632</v>
+        <v>0.0635</v>
       </c>
       <c r="E3" t="n">
         <v>0.0333333333333333</v>
@@ -477,13 +477,13 @@
         <v>200</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0421</v>
+        <v>0.0405</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0394</v>
+        <v>0.0383</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0725</v>
+        <v>0.0699</v>
       </c>
       <c r="E4" t="n">
         <v>0.0333333333333333</v>
@@ -506,13 +506,13 @@
         <v>500</v>
       </c>
       <c r="B5" t="n">
-        <v>0.044</v>
+        <v>0.0436</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0483</v>
+        <v>0.0482</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0805</v>
+        <v>0.0811</v>
       </c>
       <c r="E5" t="n">
         <v>0.0333333333333333</v>
